--- a/data/trans_orig/ProbViv_temp-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Edad-trans_orig.xlsx
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39961</t>
+          <t>40197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>47800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>68365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85666</t>
+          <t>85142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45559</t>
+          <t>46748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64724</t>
+          <t>65154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93104</t>
+          <t>93807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122773</t>
+          <t>122247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152012</t>
+          <t>153376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94575</t>
+          <t>94145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113740</t>
+          <t>112551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112160</t>
+          <t>112296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189841</t>
+          <t>188477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219080</t>
+          <t>219606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65703</t>
+          <t>65277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89658</t>
+          <t>89757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63298</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90283</t>
+          <t>90215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135248</t>
+          <t>134374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173514</t>
+          <t>171062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84230</t>
+          <t>84131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108185</t>
+          <t>108611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121264</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148249</t>
+          <t>148908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211920</t>
+          <t>214372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250186</t>
+          <t>251060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109817</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171718</t>
+          <t>177242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91639</t>
+          <t>91813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128145</t>
+          <t>128712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211224</t>
+          <t>214282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290745</t>
+          <t>295709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102740</t>
+          <t>97216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164641</t>
+          <t>164457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177338</t>
+          <t>176771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213844</t>
+          <t>213670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289196</t>
+          <t>284232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368717</t>
+          <t>365659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257984</t>
+          <t>256029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342875</t>
+          <t>338376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>312103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>532894</t>
+          <t>535925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>629449</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322281</t>
+          <t>326780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407172</t>
+          <t>409127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>448925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>500405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>796735</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>893290</t>
+          <t>890259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_temp-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3126,47 +3126,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3469,47 +3469,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3812,47 +3812,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4155,47 +4155,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5073,47 +5073,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5416,47 +5416,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5759,47 +5759,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6102,47 +6102,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16756</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12244</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21616</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22421</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17314</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29240</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33781</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28921</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38293</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28271</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40197</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>61,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47800</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77272</t>
+          <t>65440</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68365</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85142</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71088</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61615</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55322</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46748</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65154</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>34,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>43813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93807</t>
+          <t>61788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137316</t>
+          <t>122918</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122247</t>
+          <t>109954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153376</t>
+          <t>137345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75334</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95907</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>103977</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94145</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112551</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100560</t>
+          <t>93688</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88747</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112296</t>
+          <t>101705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>204537</t>
+          <t>180121</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188477</t>
+          <t>165694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219606</t>
+          <t>193085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71532</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58987</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77158</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65277</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89757</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75713</t>
+          <t>75861</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62639</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90215</t>
+          <t>86805</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152870</t>
+          <t>147392</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134374</t>
+          <t>130455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171062</t>
+          <t>164683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114240</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140182</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>64,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>96730</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84131</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108611</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135834</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>88713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148908</t>
+          <t>110387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>232564</t>
+          <t>227294</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214372</t>
+          <t>210003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251060</t>
+          <t>244231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>110627</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93084</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>126960</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>131662</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>110001</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>177242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,97%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>109819</t>
+          <t>107166</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91813</t>
+          <t>91894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128712</t>
+          <t>122019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>241482</t>
+          <t>217792</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214282</t>
+          <t>194953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295709</t>
+          <t>239400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>182018</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165685</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>199561</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>142796</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97216</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164457</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>195664</t>
+          <t>148312</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176771</t>
+          <t>133459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213670</t>
+          <t>163584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>338459</t>
+          <t>330330</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284232</t>
+          <t>308722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365659</t>
+          <t>353169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>270003</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>243222</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>292631</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>286563</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>256029</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>338376</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260623</t>
+          <t>234289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>312103</t>
+          <t>274834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>535925</t>
+          <t>493395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>633137</t>
+          <t>557944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>429869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>407241</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>456650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>574</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>378593</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>326780</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>409127</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>474239</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448925</t>
+          <t>353769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500405</t>
+          <t>394314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>852832</t>
+          <t>803185</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>793047</t>
+          <t>770531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890259</t>
+          <t>835080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
